--- a/策略调优/测试集及标注.xlsx
+++ b/策略调优/测试集及标注.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17490" windowHeight="10090"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
     <t>评测集Query</t>
   </si>
@@ -36,15 +36,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>切片方式：500</t>
-  </si>
-  <si>
-    <t>切片方式：1000</t>
-  </si>
-  <si>
-    <t>切片方式：换行符</t>
   </si>
   <si>
     <t>一、显性事实：占比60%</t>
@@ -210,45 +201,6 @@
       <t>。Agent 需指出不存在“自动离婚”条款，并召回第1079条解释诉讼离婚中分居满两年的法定适用条件。</t>
     </r>
   </si>
-  <si>
-    <t>精确率：召回的chunk中相关chunk/所有召回chunk</t>
-  </si>
-  <si>
-    <t>回答（DeepSeek V3.1）</t>
-  </si>
-  <si>
-    <t>回答（Doubao-32K）</t>
-  </si>
-  <si>
-    <t>回答（Doubao-1.5-pro-32K）</t>
-  </si>
-  <si>
-    <t>召回率：召回的相关chunk/所有相关chunk</t>
-  </si>
-  <si>
-    <t>F1score：2*精确率*召回率/（精确率+召回率）</t>
-  </si>
-  <si>
-    <t>倒数排名：最相关的chunk在chunk排位中的平均值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所有测评基准：切片方式：1.500（默认） 2.1000 3.换行符 </t>
-  </si>
-  <si>
-    <t>召回数量：7（默认）/4/10</t>
-  </si>
-  <si>
-    <t>embedding模型：large/非large（默认）</t>
-  </si>
-  <si>
-    <t>召回阈值：0.1（默认）/0.4</t>
-  </si>
-  <si>
-    <t>大模型：DeepSeek-V3.1（默认）；Doubao-32K；Doubao-1.5-pro-32K</t>
-  </si>
-  <si>
-    <t>注：此处默认即在调整某项标准时，其他的使用默认值</t>
-  </si>
 </sst>
 </file>
 
@@ -260,22 +212,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+  <fonts count="21">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -426,6 +364,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -621,27 +567,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -762,148 +693,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1430,19 +1358,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="113.545454545455" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="86.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="36.8181818181818" customWidth="1"/>
+    <col min="2" max="2" width="15.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="51.2727272727273" customWidth="1"/>
     <col min="4" max="4" width="25.6363636363636" customWidth="1"/>
     <col min="5" max="5" width="19.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="23.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1451,320 +1379,257 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" ht="28" spans="1:3">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="4" ht="28" spans="1:3">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="5" ht="28" spans="1:3">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+    <row r="6" ht="28" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+    <row r="7" ht="28" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="8" ht="28" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="9" ht="28" spans="1:3">
+      <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="10" ht="28" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" ht="42" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="42" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" ht="42" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="42" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" ht="42" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" ht="42" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" ht="14.75" spans="1:6">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" ht="14.75" spans="1:6">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+    <row r="23" ht="42" spans="1:3">
+      <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="B23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" ht="28" spans="1:3">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
+    <row r="26" spans="1:3">
+      <c r="B26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
